--- a/swift-crm-automation/data/Input_data.xlsx
+++ b/swift-crm-automation/data/Input_data.xlsx
@@ -1,38 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\QD2982\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New VI UAT PROJECT\WIP\Automation Folder\VI Demo 31.05.2026\VI Demo\swift-crm-automation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0373A63-0DCF-4093-867D-63DBD4430AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27A0CD1-7F62-40CC-8443-2AE8F2CE275B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{ABFECE7D-A40B-4DF2-B053-BF2EDF7965DD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{ABFECE7D-A40B-4DF2-B053-BF2EDF7965DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Input excel" sheetId="1" r:id="rId1"/>
     <sheet name="Recharge Plans" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="38">
-  <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
   <si>
     <t>MSISDN</t>
   </si>
@@ -52,12 +58,6 @@
     <t>Vi App</t>
   </si>
   <si>
-    <t>COR4055772</t>
-  </si>
-  <si>
-    <t>Test@123456789!</t>
-  </si>
-  <si>
     <t>ODI</t>
   </si>
   <si>
@@ -133,20 +133,14 @@
     <t>Recharge</t>
   </si>
   <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>yes</t>
+    <t>No</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,24 +166,15 @@
       <name val="Poppins"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Poppins"/>
     </font>
     <font>
-      <sz val="7"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Poppins"/>
     </font>
   </fonts>
   <fills count="7">
@@ -230,7 +215,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -239,30 +224,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -314,74 +275,78 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -694,389 +659,247 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3CD6BEF-943B-46C2-A3A0-9079289648AA}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="25.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultColWidth="25.42578125" defaultRowHeight="21.75" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.81640625" customWidth="1"/>
-    <col min="4" max="4" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="16.26953125" customWidth="1"/>
+    <col min="1" max="1" width="26.85546875" style="17" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" style="17" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" style="17" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" style="17" customWidth="1"/>
+    <col min="6" max="7" width="16.28515625" style="17" customWidth="1"/>
+    <col min="8" max="16384" width="25.42578125" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="22" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" s="16" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A2" s="12">
+        <v>8399930232</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="C2" s="13">
+        <v>149</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>7</v>
       </c>
+      <c r="E2" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" ht="22" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="7">
+    <row r="3" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="12">
         <v>8399930232</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="9">
+      <c r="B3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="13">
         <v>149</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="22" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="7">
-        <v>9610781347</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="9">
-        <v>299</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="10"/>
-    </row>
-    <row r="4" spans="1:9" ht="22" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="7">
-        <v>9090</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="9">
-        <v>149</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="22" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="7">
-        <v>1212121212121210</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="9">
-        <v>299</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="22" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="7">
-        <v>6390080177</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="9">
-        <v>2204</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="22" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="20">
-        <v>7095361541</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="9">
-        <v>199</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>37</v>
+      <c r="D3" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{033F518D-6B94-4A4D-8B91-E10659AB44F0}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{44E854F3-A3F2-4E70-AEBA-8DD642A8F4F1}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{5E4112B8-F9F3-4FFF-9A34-310CCCFA24C7}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{9E51874F-89D5-4517-84E5-0CA28F26260F}"/>
-    <hyperlink ref="B6" r:id="rId5" xr:uid="{F063B37D-4088-44C8-AF75-903379FDC0E6}"/>
-    <hyperlink ref="B7" r:id="rId6" xr:uid="{E7DF3EBE-28F9-43DF-A8AD-2104193D6986}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId7"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{480D6692-CB6D-4C7B-9801-B3A4602D5800}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="19"/>
-    <col min="2" max="2" width="18.54296875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="21.7265625" style="19" customWidth="1"/>
-    <col min="4" max="4" width="28.54296875" style="19" customWidth="1"/>
-    <col min="5" max="5" width="9.1796875" style="19"/>
-    <col min="6" max="6" width="26.7265625" style="19" customWidth="1"/>
-    <col min="7" max="7" width="68.1796875" style="19" customWidth="1"/>
-    <col min="8" max="16384" width="9.1796875" style="19"/>
+    <col min="1" max="1" width="9.140625" style="10"/>
+    <col min="2" max="2" width="18.5703125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="10"/>
+    <col min="6" max="6" width="26.7109375" style="10" customWidth="1"/>
+    <col min="7" max="7" width="68.140625" style="10" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:7" ht="22.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="F1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="G1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="13" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7">
+        <v>199</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="D2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="E2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="F2" s="8" t="s">
         <v>18</v>
       </c>
+      <c r="G2" s="9" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" ht="65" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="15">
-        <v>1</v>
-      </c>
-      <c r="B2" s="16">
-        <v>199</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="16" t="s">
+    <row r="3" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7">
+        <v>149</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="D3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G3" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="65" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="15">
-        <v>2</v>
-      </c>
-      <c r="B3" s="16">
-        <v>149</v>
-      </c>
-      <c r="C3" s="10" t="s">
+    <row r="4" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7">
+        <v>299</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="G4" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7">
+        <v>719</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="17" t="s">
+      <c r="D5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G5" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="65" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="15">
-        <v>3</v>
-      </c>
-      <c r="B4" s="16">
-        <v>299</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="16" t="s">
+    <row r="6" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7">
+        <v>369</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G6" s="9" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="65" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="15">
-        <v>4</v>
-      </c>
-      <c r="B5" s="16">
-        <v>719</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="65" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="15">
-        <v>5</v>
-      </c>
-      <c r="B6" s="16">
-        <v>369</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/swift-crm-automation/data/Input_data.xlsx
+++ b/swift-crm-automation/data/Input_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New VI UAT PROJECT\WIP\Automation Folder\VI Demo 31.05.2026\VI Demo\swift-crm-automation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27A0CD1-7F62-40CC-8443-2AE8F2CE275B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB9812D-34A1-4C3D-8EE3-C5FC24CF6BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{ABFECE7D-A40B-4DF2-B053-BF2EDF7965DD}"/>
+    <workbookView xWindow="2295" yWindow="2295" windowWidth="15375" windowHeight="7785" xr2:uid="{ABFECE7D-A40B-4DF2-B053-BF2EDF7965DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Input excel" sheetId="1" r:id="rId1"/>
@@ -714,7 +714,7 @@
         <v>7</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.6">

--- a/swift-crm-automation/data/Input_data.xlsx
+++ b/swift-crm-automation/data/Input_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New VI UAT PROJECT\WIP\Automation Folder\VI Demo 31.05.2026\VI Demo\swift-crm-automation\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\QD2245\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB9812D-34A1-4C3D-8EE3-C5FC24CF6BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D296DEDA-3FD4-4C09-A083-23A400E72561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="15375" windowHeight="7785" xr2:uid="{ABFECE7D-A40B-4DF2-B053-BF2EDF7965DD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{ABFECE7D-A40B-4DF2-B053-BF2EDF7965DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Input excel" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
   <si>
     <t>MSISDN</t>
   </si>
@@ -58,9 +58,6 @@
     <t>Vi App</t>
   </si>
   <si>
-    <t>ODI</t>
-  </si>
-  <si>
     <t>Yes</t>
   </si>
   <si>
@@ -106,12 +103,6 @@
     <t>ULD</t>
   </si>
   <si>
-    <t>UL+1.5GB/Day+HERO+100SMS/Day||56D</t>
-  </si>
-  <si>
-    <t>Rs 479 recharged! Enjoy 1.5GB/Day + Unlimited Calls + 100SMS/Day. Valid for 56 Days. Click bit.ly/GetViApp to check balance, expiry, best offers &amp; more.</t>
-  </si>
-  <si>
     <t>UL+1.5GB/Day+100SMS/Day||28D</t>
   </si>
   <si>
@@ -134,6 +125,27 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>ODI/ASM/NE/HP/JNK/MUM</t>
+  </si>
+  <si>
+    <t>UL+300SMS+1GB||28D</t>
+  </si>
+  <si>
+    <t>Rs179 recharged! Enjoy 1GB + Unlimited Calls + 300 SMS. Validity: 28 Days. Click bit.ly/GetViApp to check balance,expiry,offers &amp; more</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>UL+1GB+100SMS||28D</t>
+  </si>
+  <si>
+    <t>Rs 149 recharge done! Unlimited Calls+100SMS+1GB. Validity 28D.Click bit.ly/GetViApp for more information</t>
+  </si>
+  <si>
+    <t>ASM</t>
   </si>
 </sst>
 </file>
@@ -231,6 +243,17 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -271,21 +294,6 @@
       </right>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -294,57 +302,60 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -662,82 +673,82 @@
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultColWidth="25.42578125" defaultRowHeight="21.75" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="26.85546875" style="17" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" style="17" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" style="17" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" style="17" customWidth="1"/>
-    <col min="6" max="7" width="16.28515625" style="17" customWidth="1"/>
-    <col min="8" max="16384" width="25.42578125" style="17"/>
+    <col min="1" max="1" width="26.85546875" style="14" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" style="14" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.140625" style="14" customWidth="1"/>
+    <col min="6" max="7" width="16.28515625" style="14" customWidth="1"/>
+    <col min="8" max="16384" width="25.42578125" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="16" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:7" s="17" customFormat="1" ht="22.5" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="11" t="s">
+      <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="12">
+    <row r="2" spans="1:7" ht="22.5" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A2" s="2">
         <v>8399930232</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="4">
+        <v>149</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="13">
-        <v>149</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>7</v>
+      <c r="E2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="12">
-        <v>8399930232</v>
-      </c>
-      <c r="B3" s="12" t="s">
+    <row r="3" spans="1:7" ht="22.5" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A3" s="2">
+        <v>7039719774</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="4">
+        <v>179</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="13">
-        <v>149</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>31</v>
+      <c r="F3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -748,158 +759,182 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{480D6692-CB6D-4C7B-9801-B3A4602D5800}">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="21.75" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="10"/>
-    <col min="2" max="2" width="18.5703125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="10" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" style="10" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="10"/>
-    <col min="6" max="6" width="26.7109375" style="10" customWidth="1"/>
-    <col min="7" max="7" width="68.140625" style="10" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="10"/>
+    <col min="1" max="1" width="9.140625" style="18"/>
+    <col min="2" max="2" width="18.5703125" style="18" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="18" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" style="18" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="18"/>
+    <col min="6" max="6" width="26.7109375" style="18" customWidth="1"/>
+    <col min="7" max="7" width="68.140625" style="18" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" ht="22.5" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A2" s="10">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11">
+        <v>199</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>14</v>
       </c>
+      <c r="D2" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7">
-        <v>199</v>
-      </c>
-      <c r="C2" s="7" t="s">
+    <row r="3" spans="1:7" ht="44.25" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A3" s="10">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11">
+        <v>149</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E3" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A4" s="10">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11">
+        <v>299</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A5" s="10">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11">
+        <v>719</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A6" s="10">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11">
+        <v>369</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>19</v>
+      <c r="F6" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7">
-        <v>149</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="7" t="s">
+    <row r="7" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A7" s="10">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11">
+        <v>179</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7">
-        <v>299</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7">
-        <v>719</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7">
-        <v>369</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>29</v>
+      <c r="F7" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/swift-crm-automation/data/Input_data.xlsx
+++ b/swift-crm-automation/data/Input_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\QD2245\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New VI UAT PROJECT\WIP\Automation Folder\VI Demo 31.05.2026\VI Demo\swift-crm-automation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D296DEDA-3FD4-4C09-A083-23A400E72561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A8FBF7-C846-4185-91BF-5F1C82855670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{ABFECE7D-A40B-4DF2-B053-BF2EDF7965DD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{ABFECE7D-A40B-4DF2-B053-BF2EDF7965DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Input excel" sheetId="1" r:id="rId1"/>
@@ -139,13 +139,13 @@
     <t>DE</t>
   </si>
   <si>
-    <t>UL+1GB+100SMS||28D</t>
-  </si>
-  <si>
-    <t>Rs 149 recharge done! Unlimited Calls+100SMS+1GB. Validity 28D.Click bit.ly/GetViApp for more information</t>
-  </si>
-  <si>
     <t>ASM</t>
+  </si>
+  <si>
+    <t>UL+1GB+300SMS||28D</t>
+  </si>
+  <si>
+    <t>Rs 149 recharge done! Unlimited Calls+300SMS+1GB. Validity 28D.Click bit.ly/GetViApp for more information</t>
   </si>
 </sst>
 </file>
@@ -710,7 +710,7 @@
         <v>8399930232</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C2" s="4">
         <v>149</v>
@@ -835,10 +835,10 @@
         <v>20</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.65">

--- a/swift-crm-automation/data/Input_data.xlsx
+++ b/swift-crm-automation/data/Input_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New VI UAT PROJECT\WIP\Automation Folder\VI Demo 31.05.2026\VI Demo\swift-crm-automation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A8FBF7-C846-4185-91BF-5F1C82855670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665D137E-8DC7-4CAB-96A0-1EFCD8EA1A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{ABFECE7D-A40B-4DF2-B053-BF2EDF7965DD}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
   <si>
     <t>MSISDN</t>
   </si>
@@ -127,15 +127,6 @@
     <t>No</t>
   </si>
   <si>
-    <t>ODI/ASM/NE/HP/JNK/MUM</t>
-  </si>
-  <si>
-    <t>UL+300SMS+1GB||28D</t>
-  </si>
-  <si>
-    <t>Rs179 recharged! Enjoy 1GB + Unlimited Calls + 300 SMS. Validity: 28 Days. Click bit.ly/GetViApp to check balance,expiry,offers &amp; more</t>
-  </si>
-  <si>
     <t>DE</t>
   </si>
   <si>
@@ -146,6 +137,18 @@
   </si>
   <si>
     <t>Rs 149 recharge done! Unlimited Calls+300SMS+1GB. Validity 28D.Click bit.ly/GetViApp for more information</t>
+  </si>
+  <si>
+    <t>RJ/ASM/NE/HP/JNK</t>
+  </si>
+  <si>
+    <t>UL+300SMS+1GB||24D</t>
+  </si>
+  <si>
+    <t>Rs179 recharged! Enjoy 1GB + Unlimited Calls + 300 SMS. Validity: 24 Days. Click bit.ly/GetViApp to check balance,expiry,offers &amp; more</t>
+  </si>
+  <si>
+    <t>ODI/ASM/RAJ/HP/JNK/MUM</t>
   </si>
 </sst>
 </file>
@@ -710,7 +713,7 @@
         <v>8399930232</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C2" s="4">
         <v>149</v>
@@ -733,7 +736,7 @@
         <v>7039719774</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C3" s="4">
         <v>179</v>
@@ -759,7 +762,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{480D6692-CB6D-4C7B-9801-B3A4602D5800}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="21.75" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="18"/>
@@ -835,21 +838,21 @@
         <v>20</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.65">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="44.25" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A4" s="10">
         <v>3</v>
       </c>
       <c r="B4" s="11">
-        <v>299</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>19</v>
+        <v>145</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>15</v>
@@ -857,11 +860,11 @@
       <c r="E4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="11" t="s">
-        <v>21</v>
+      <c r="F4" s="12" t="s">
+        <v>31</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.65">
@@ -869,9 +872,9 @@
         <v>4</v>
       </c>
       <c r="B5" s="11">
-        <v>719</v>
-      </c>
-      <c r="C5" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="11" t="s">
@@ -880,11 +883,11 @@
       <c r="E5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>23</v>
+      <c r="F5" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.65">
@@ -892,22 +895,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="11">
-        <v>369</v>
+        <v>719</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.65">
@@ -915,10 +918,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="11">
-        <v>179</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>29</v>
+        <v>369</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>15</v>
@@ -927,10 +930,33 @@
         <v>16</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>31</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A8" s="10">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11">
+        <v>179</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
